--- a/docentes/Martínez Castillo Columba - Estadisticos 20221.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -88,6 +94,12 @@
     <t>HERRERA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
@@ -95,6 +107,12 @@
   </si>
   <si>
     <t>SIERRA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
   <si>
     <t>REYLI</t>
@@ -953,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -985,16 +1003,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920378</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1008,16 +1026,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920092</v>
+        <v>21330051920103</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1031,25 +1049,71 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920046</v>
+        <v>20330051920378</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920092</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920046</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="G4">
-        <v>2</v>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20221.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,51 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
   </si>
 </sst>
 </file>
@@ -691,16 +646,19 @@
         <v>27</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>27</v>
       </c>
-      <c r="E2">
-        <v>27</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -714,16 +672,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -737,16 +698,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -760,16 +724,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -783,16 +750,19 @@
         <v>15</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>15</v>
       </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -874,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -900,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -926,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>81.25</v>
+        <v>96.88</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -952,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1001,121 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920078</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920103</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920378</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920092</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920046</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20221.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20221.xlsx
@@ -827,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +853,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -905,7 +905,7 @@
         <v>96.88</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
